--- a/Tabela2_pesos.xlsx
+++ b/Tabela2_pesos.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2.375113</v>
+        <v>1.597049</v>
       </c>
     </row>
     <row r="4">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2.696487</v>
+        <v>2.503513</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1.001938</v>
+        <v>1.295083</v>
       </c>
     </row>
   </sheetData>
